--- a/Analysis/Phase1_Results.xlsx
+++ b/Analysis/Phase1_Results.xlsx
@@ -1,15 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10201"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM/LLM-Generation-Intentionally-Vulnerable-Dockerfiles/Analysis/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE892CF9-4B85-2C45-837B-753F327059AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$55</definedName>
+  </definedNames>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -328,8 +337,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -379,59 +387,59 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -442,10 +450,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -483,71 +491,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -575,7 +583,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -598,11 +606,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -611,13 +619,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -627,7 +635,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -636,7 +644,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -645,7 +653,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -653,10 +661,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -721,23 +729,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="2" width="12.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="33.75">
+    <row r="1" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -760,7 +765,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="255.75">
+    <row r="2" spans="1:7" ht="255.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
@@ -783,7 +788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="353.25">
+    <row r="3" spans="1:7" ht="353.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
@@ -806,7 +811,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="394.5">
+    <row r="4" spans="1:7" ht="394.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -829,7 +834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="283.5">
+    <row r="5" spans="1:7" ht="283.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
@@ -852,7 +857,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="311.25">
+    <row r="6" spans="1:7" ht="311.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>7</v>
       </c>
@@ -875,7 +880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="242.25">
+    <row r="7" spans="1:7" ht="242.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -898,7 +903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="394.5">
+    <row r="8" spans="1:7" ht="394.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>26</v>
       </c>
@@ -921,7 +926,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="450">
+    <row r="9" spans="1:7" ht="409.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>26</v>
       </c>
@@ -944,7 +949,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="228">
+    <row r="10" spans="1:7" ht="228" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>26</v>
       </c>
@@ -967,7 +972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="422.25">
+    <row r="11" spans="1:7" ht="409.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>26</v>
       </c>
@@ -990,7 +995,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="283.5">
+    <row r="12" spans="1:7" ht="283.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>26</v>
       </c>
@@ -1013,7 +1018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="283.5">
+    <row r="13" spans="1:7" ht="283.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>26</v>
       </c>
@@ -1036,7 +1041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="325.5">
+    <row r="14" spans="1:7" ht="325.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
@@ -1059,7 +1064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="297.75">
+    <row r="15" spans="1:7" ht="297.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>37</v>
       </c>
@@ -1082,7 +1087,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="283.5">
+    <row r="16" spans="1:7" ht="283.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
@@ -1105,7 +1110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="200.25">
+    <row r="17" spans="1:7" ht="200.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
@@ -1128,7 +1133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="270">
+    <row r="18" spans="1:7" ht="270" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>37</v>
       </c>
@@ -1151,7 +1156,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="339">
+    <row r="19" spans="1:7" ht="339" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
@@ -1174,7 +1179,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25">
+    <row r="20" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>50</v>
       </c>
@@ -1197,7 +1202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25">
+    <row r="21" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>50</v>
       </c>
@@ -1220,7 +1225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25">
+    <row r="22" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>50</v>
       </c>
@@ -1243,7 +1248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="17.25">
+    <row r="23" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>50</v>
       </c>
@@ -1266,7 +1271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25">
+    <row r="24" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>50</v>
       </c>
@@ -1289,7 +1294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="17.25">
+    <row r="25" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>50</v>
       </c>
@@ -1312,7 +1317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25">
+    <row r="26" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>63</v>
       </c>
@@ -1335,7 +1340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="17.25">
+    <row r="27" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>63</v>
       </c>
@@ -1358,7 +1363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25">
+    <row r="28" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>63</v>
       </c>
@@ -1381,7 +1386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="17.25">
+    <row r="29" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>63</v>
       </c>
@@ -1404,7 +1409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="17.25">
+    <row r="30" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>63</v>
       </c>
@@ -1427,7 +1432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25">
+    <row r="31" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>63</v>
       </c>
@@ -1450,7 +1455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25">
+    <row r="32" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>75</v>
       </c>
@@ -1473,7 +1478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="17.25">
+    <row r="33" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>75</v>
       </c>
@@ -1496,7 +1501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25">
+    <row r="34" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>75</v>
       </c>
@@ -1513,7 +1518,7 @@
       <c r="F34" s="7"/>
       <c r="G34" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
+    <row r="35" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>75</v>
       </c>
@@ -1536,7 +1541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
+    <row r="36" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>75</v>
       </c>
@@ -1559,7 +1564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
+    <row r="37" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>75</v>
       </c>
@@ -1578,7 +1583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
+    <row r="38" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>82</v>
       </c>
@@ -1597,7 +1602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
+    <row r="39" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>82</v>
       </c>
@@ -1620,7 +1625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
+    <row r="40" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>82</v>
       </c>
@@ -1641,7 +1646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
+    <row r="41" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>82</v>
       </c>
@@ -1658,7 +1663,7 @@
       <c r="F41" s="7"/>
       <c r="G41" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
+    <row r="42" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>82</v>
       </c>
@@ -1681,7 +1686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
+    <row r="43" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>82</v>
       </c>
@@ -1704,7 +1709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
+    <row r="44" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>88</v>
       </c>
@@ -1727,7 +1732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
+    <row r="45" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>88</v>
       </c>
@@ -1750,7 +1755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
+    <row r="46" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>88</v>
       </c>
@@ -1773,7 +1778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
+    <row r="47" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
         <v>88</v>
       </c>
@@ -1796,7 +1801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
+    <row r="48" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>88</v>
       </c>
@@ -1819,7 +1824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
+    <row r="49" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>88</v>
       </c>
@@ -1842,7 +1847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
+    <row r="50" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>98</v>
       </c>
@@ -1858,12 +1863,11 @@
       <c r="E50" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="F50" s="10"/>
       <c r="G50" s="8">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
+    <row r="51" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
         <v>98</v>
       </c>
@@ -1884,7 +1888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
+    <row r="52" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
         <v>98</v>
       </c>
@@ -1903,7 +1907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
+    <row r="53" spans="1:7" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
         <v>98</v>
       </c>
@@ -1926,7 +1930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
+    <row r="54" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
         <v>98</v>
       </c>
@@ -1941,9 +1945,11 @@
       </c>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
-      <c r="G54" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
+      <c r="G54" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>98</v>
       </c>
@@ -1958,9 +1964,20 @@
       </c>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
-      <c r="G55" s="8"/>
+      <c r="G55" s="8">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G55" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Gemini3-Pro"/>
+        <filter val="Gpt5.2-Thinking"/>
+        <filter val="Gpt5.2-Thinking-Web"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Analysis/Phase1_Results.xlsx
+++ b/Analysis/Phase1_Results.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM/LLM-Generation-Intentionally-Vulnerable-Dockerfiles/Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE892CF9-4B85-2C45-837B-753F327059AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49AA9ED9-B18E-B249-8ABB-A8C702D96282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17780" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$55</definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="103">
   <si>
     <t>CVE-ID</t>
   </si>
@@ -387,7 +388,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -427,6 +428,9 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1979,5 +1983,72 @@
     </filterColumn>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53908833-0434-A84C-B73A-F697FFD9FDE3}">
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>